--- a/INPUT/test.xlsx
+++ b/INPUT/test.xlsx
@@ -1298,11 +1298,11 @@
         <v>120</v>
       </c>
       <c r="E3" s="8">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="F3" s="9">
         <f>D3+E3</f>
-        <v>140</v>
+        <v>120</v>
       </c>
       <c r="G3" s="10">
         <v>9854.03</v>
